--- a/Гайковерты_ADENIS.xlsx
+++ b/Гайковерты_ADENIS.xlsx
@@ -9,15 +9,12 @@
   <sheets>
     <sheet name="Гайковерты" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Листочек" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Куда вписать вес" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Гайковерты'!$A$4:$G$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Гайковерты'!$A$4:$F$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Гайковерты'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Гайковерты'!$A$1:$G$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Листочек'!$A$4:$E$13</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Листочек'!$A$1:$E$19</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Куда вписать вес'!$A$1:$D$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Гайковерты'!$A$1:$F$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Листочек'!$A$1:$D$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -82,7 +79,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -111,11 +108,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDECEC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFF6D8"/>
       </patternFill>
     </fill>
@@ -124,13 +116,8 @@
         <fgColor rgb="003D4A4F"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3BF"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -166,11 +153,88 @@
         <color rgb="00E6D7A2"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E6D7A2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E6D7A2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E6D7A2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E6D7A2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E6D7A2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E6D7A2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E6D7A2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E6D7A2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D0D5D8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D0D5D8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D5D8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D0D5D8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D5D8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D5D8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -187,50 +251,45 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -315,7 +374,47 @@
   <commentList>
     <comment ref="E5" authorId="0" shapeId="0">
       <text>
-        <t>На карточке товара adenis.su вес не написан. Цифра 69 кг переписана с вашего листочка и стоит только напротив модели 2500. Это может быть вес партии, а не одной коробки — на листочке у других моделей написано «шт».</t>
+        <t>На листочке написано: 6,9 кг</t>
+      </text>
+    </comment>
+    <comment ref="E6" authorId="0" shapeId="0">
+      <text>
+        <t>На листочке написано: 6,8 кг</t>
+      </text>
+    </comment>
+    <comment ref="E7" authorId="0" shapeId="0">
+      <text>
+        <t>На листочке написано: 9,3 кг</t>
+      </text>
+    </comment>
+    <comment ref="E8" authorId="0" shapeId="0">
+      <text>
+        <t>На листочке написано: 6,9 кг</t>
+      </text>
+    </comment>
+    <comment ref="E9" authorId="0" shapeId="0">
+      <text>
+        <t>На листочке написано: 8,2 кг</t>
+      </text>
+    </comment>
+    <comment ref="E10" authorId="0" shapeId="0">
+      <text>
+        <t>На листочке написано: 6 кг</t>
+      </text>
+    </comment>
+    <comment ref="E11" authorId="0" shapeId="0">
+      <text>
+        <t>На листочке написано: 5,7 кг</t>
+      </text>
+    </comment>
+    <comment ref="E12" authorId="0" shapeId="0">
+      <text>
+        <t>На листочке написано: 5,6 кг</t>
+      </text>
+    </comment>
+    <comment ref="E13" authorId="0" shapeId="0">
+      <text>
+        <t>На листочке написано: 5 кг</t>
       </text>
     </comment>
   </commentList>
@@ -612,16 +711,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="62" customWidth="1" min="6" max="6"/>
-    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="64" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -634,7 +732,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Названия и размеры коробок взяты с карточек товаров на сайте https://adenis.su/   ·   дата выгрузки: 7 октября 2026</t>
+          <t>Названия и коробки — с карточек на https://adenis.su/   ·   вес каждой модели — с вашего листочка, в килограммах   ·   7 октября 2026</t>
         </is>
       </c>
     </row>
@@ -663,7 +761,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Вес одной штуки</t>
+          <t>Вес, кг</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -671,13 +769,8 @@
           <t>Ссылка на карточку на сайте</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Что написано на листочке</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
+    </row>
+    <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="n">
         <v>1</v>
       </c>
@@ -696,59 +789,44 @@
           <t>42 × 32 × 14</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>69 кг — только с листочка.
-На сайте вес не указан.</t>
-        </is>
+      <c r="E5" s="6" t="n">
+        <v>6.9</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
           <t>https://adenis.su/tproduct/234640101402-gaikovert-2500-nm</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>2500 — 69 кг</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="9" t="n">
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>ADENIS</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Гайковерт 2200 Нм</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>42 × 32 × 14</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>На сайте не указан</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="E6" s="6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>https://adenis.su/tproduct/679794027832-gaikovert-2200-nm</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>2200 — 68 (единица не подписана, похоже на штуки)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
+    </row>
+    <row r="7" ht="24" customHeight="1">
       <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
@@ -767,58 +845,44 @@
           <t>42 × 32 × 14</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>На сайте не указан</t>
-        </is>
+      <c r="E7" s="6" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
           <t>https://adenis.su/tproduct/624931412933-gaikovert-mt-2100-nm</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>MT2100 — 93 шт</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="9" t="n">
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>ADENIS</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Гайковерт 2100 Нм</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>42 × 32 × 14</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>На сайте не указан</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="E8" s="6" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>https://adenis.su/tproduct/844179078152-gaikovert-2100-nm</t>
         </is>
       </c>
-      <c r="G8" s="13" t="inlineStr">
-        <is>
-          <t>2100 — 69 шт</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
+    </row>
+    <row r="9" ht="24" customHeight="1">
       <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
@@ -837,58 +901,44 @@
           <t>42 × 32 × 14</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>На сайте не указан</t>
-        </is>
+      <c r="E9" s="6" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
           <t>https://adenis.su/tproduct/261441232642-gaikovert-2000-nm</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>2000 — 82 (единица не подписана, похоже на штуки)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="9" t="n">
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>ADENIS</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Гайковерт 1500 Нм</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>42 × 32 × 14</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>На сайте не указан</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="E10" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>https://adenis.su/tproduct/643780222952-gaikovert-1500-nm</t>
         </is>
       </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t>1500 — 6 (единица не подписана, похоже на штуки)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
+    </row>
+    <row r="11" ht="24" customHeight="1">
       <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
@@ -907,58 +957,44 @@
           <t>38 × 30 × 14</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>На сайте не указан</t>
-        </is>
+      <c r="E11" s="6" t="n">
+        <v>5.7</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
           <t>https://adenis.su/tproduct/564940518092-gaikovert-1400-nm-s-osnastkoi</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>1400 — 57 (единица не подписана, похоже на штуки)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="9" t="n">
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>ADENIS</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Гайковерт 1200 Нм с оснасткой</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>38 × 30 × 12</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>На сайте не указан</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="E12" s="6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>https://adenis.su/tproduct/133476019772-gaikovert-1200-nm-s-osnastkoi</t>
         </is>
       </c>
-      <c r="G12" s="13" t="inlineStr">
-        <is>
-          <t>1200 — 56 шт</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
+    </row>
+    <row r="13" ht="24" customHeight="1">
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
@@ -977,119 +1013,93 @@
           <t>42 × 32 × 14</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>На сайте не указан</t>
-        </is>
+      <c r="E13" s="6" t="n">
+        <v>5</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
           <t>https://adenis.su/tproduct/950709964723-gaikovert-mt-800-nm</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>MT 800 — 5 (единица не подписана, похоже на штуки)</t>
-        </is>
-      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Как читать эту таблицу</t>
         </is>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>1. Бренд у всех моделей один: ADENIS. На сайте это девять моделей от 800 до 2500 Н·м.</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="16" t="n"/>
-      <c r="D16" s="16" t="n"/>
-      <c r="E16" s="16" t="n"/>
-      <c r="F16" s="16" t="n"/>
-      <c r="G16" s="16" t="n"/>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>1. Бренд у всех моделей один: ADENIS. Названия взяты с сайта adenis.su.</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="n"/>
+      <c r="C16" s="19" t="n"/>
+      <c r="D16" s="19" t="n"/>
+      <c r="E16" s="19" t="n"/>
+      <c r="F16" s="20" t="n"/>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>2. Размер коробки взят из строки «Комплектация» на карточке каждого товара (там написано «картонный короб …»). Это размер транспортной коробки, не пластикового кейса.</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
-      <c r="G17" s="16" t="n"/>
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>2. Размер коробки взят из строки «Комплектация» на карточке товара (там написано «картонный короб»). Это размер транспортной коробки.</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="n"/>
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="19" t="n"/>
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="20" t="n"/>
     </row>
     <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>3. Вес одной штуки на сайте adenis.su ни у одной модели не указан. Зелёная ячейка — единственная цифра в килограммах с вашего листочка (модель 2500, 69 кг). Красные ячейки — вес на сайте не найден.</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="16" t="n"/>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>4. Столбец «Что написано на листочке» — это цифры с фотографии. Где подписано «шт», это количество штук, а не вес. Где единица не подписана (5, 6, 57, 68, 82), я оставил цифру как есть: по соседним строкам это тоже похоже на количество.</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="16" t="n"/>
-      <c r="F19" s="16" t="n"/>
-      <c r="G19" s="16" t="n"/>
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>3. Вес — с вашего листочка, в килограммах, для каждой модели. Запятая на бумаге маленькая, поэтому записано 6,9 кг, а не 69 кг. У моделей МТ 800 и 1500 на листочке целые числа: 5 кг и 6 кг.</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="19" t="n"/>
+      <c r="F18" s="20" t="n"/>
+    </row>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>4. На листочке внизу отдельно записаны три размера: 42×32×13, 38×30×14 и 38×30×12. На сайте у большинства моделей коробка 42×32×14 (высота 14 см, не 13). Размеры 38×30×14 и 38×30×12 совпадают с моделями 1400 и 1200.</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="n"/>
+      <c r="C19" s="19" t="n"/>
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="20" t="n"/>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>5. На листочке внизу отдельно, без привязки к модели, записаны три размера: 42×32×13, 38×30×14 и 38×30×12. На сайте у большинства моделей коробка 42×32×14 (высота 14 см, не 13). Размеры 38×30×14 и 38×30×12 на сайте есть: они у моделей 1400 и 1200.</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="16" t="n"/>
-    </row>
-    <row r="21" ht="48" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>6. Синие надписи в столбце «Ссылка» кликабельны: нажатие открывает карточку этой модели на adenis.su.</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="16" t="n"/>
-      <c r="E21" s="16" t="n"/>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="16" t="n"/>
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>5. Синие надписи в столбце «Ссылка» открывают карточку этой модели на сайте.</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="n"/>
+      <c r="C20" s="19" t="n"/>
+      <c r="D20" s="19" t="n"/>
+      <c r="E20" s="19" t="n"/>
+      <c r="F20" s="20" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G13"/>
-  <mergeCells count="9">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A19:G19"/>
+  <autoFilter ref="A4:F13"/>
+  <mergeCells count="8">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId1"/>
@@ -1106,7 +1116,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;LADENIS — гайковёрты</oddHeader>
-    <oddFooter>&amp;LИсточник названий и коробок: adenis.su&amp;RСтраница &amp;P из &amp;N</oddFooter>
+    <oddFooter>&amp;LВес — с листочка, кг. Коробки и названия — с adenis.su&amp;RСтраница &amp;P из &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1123,632 +1133,322 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="17" t="inlineStr">
-        <is>
-          <t>Как прочитан ваш листочек</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
-        <is>
-          <t>Это расшифровка фотографии. Если какая-то цифра прочитана не так — поправьте её прямо в ячейке.</t>
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Вес с листочка — килограммы по каждой модели</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Каждая цифра справа от модели — это вес в кг. Если запятая прочитана не там, поправьте жёлтую ячейку на листе «Гайковерты».</t>
         </is>
       </c>
     </row>
     <row r="3" ht="8" customHeight="1"/>
-    <row r="4" ht="32" customHeight="1">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Как написано на листочке</t>
+          <t>Модель на листочке</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Какая модель на сайте</t>
+          <t>Название на сайте</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Цифра</t>
+          <t>Вес, кг</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Что подписано рядом</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Куда это попало в таблице</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>2500   69 кг.</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
+          <t>Как прочитана запись</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Гайковерт 2500 Нм</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>кг</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Столбец «Вес» и столбец «Листочек»</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>MT2100   93 шт</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="C5" s="6" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>6,9 кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Гайковерт 2200 Нм</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>6,8 кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>MT 2100</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Гайковерт МТ 2100 Нм</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>Столбец «Листочек» — это количество, не вес</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>1200   56 шт</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="C7" s="6" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>9,3 кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Гайковерт 2100 Нм</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>6,9 кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Гайковерт 2000 Нм</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>8,2 кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Гайковерт 1500 Нм</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>6 кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Гайковерт 1400 Нм с оснасткой</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>5,7 кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>Гайковерт 1200 Нм с оснасткой</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>Столбец «Листочек» — это количество, не вес</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>1400   57</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>Гайковерт 1400 Нм с оснасткой</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>не подписано</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>Оставлено как есть. Рядом у других строк написано «шт»</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>MT 800   5</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="C12" s="6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>5,6 кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>MT 800</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Гайковерт МТ 800 Нм</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>не подписано</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>Оставлено как есть. Рядом у других строк написано «шт»</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>1500   6</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>Гайковерт 1500 Нм</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>не подписано</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>Оставлено как есть. Рядом у других строк написано «шт»</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>2000   82</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Гайковерт 2000 Нм</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>не подписано</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>Оставлено как есть. Рядом у других строк написано «шт»</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>2200   68</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>Гайковерт 2200 Нм</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>не подписано</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>Оставлено как есть. Рядом у других строк написано «шт»</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>2100   69 шт</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Гайковерт 2100 Нм</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>Столбец «Листочек» — это количество, не вес</t>
+      <c r="C13" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>5 кг</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>Размеры коробок, записанные внизу листочка отдельно от моделей</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Размеры коробок внизу листочка (они не привязаны к строке модели)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>Как на листочке</t>
         </is>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>Похожая коробка на сайте</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>У каких моделей на сайте</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="D16" s="21" t="n"/>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>42 × 32 × 13</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>42 × 32 × 14  (на сайте высота 14, не 13)</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>2500, 2200, МТ 2100, 2100, 2000, 1500, МТ 800</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="D17" s="21" t="n"/>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>38 × 30 × 14</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>38 × 30 × 14  (совпадает)</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>1400 Нм с оснасткой</t>
         </is>
       </c>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="D18" s="21" t="n"/>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>38 × 30 × 12</t>
         </is>
       </c>
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>38 × 30 × 12  (совпадает)</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>1200 Нм с оснасткой</t>
         </is>
       </c>
+      <c r="D19" s="21" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E13"/>
-  <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="7">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C17:D17"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="002E7D4F"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="64" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="17" t="inlineStr">
-        <is>
-          <t>Пустые ячейки для веса — впишите сами, когда взвесите коробку</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
-        <is>
-          <t>На сайте веса нет. Жёлтые ячейки можно заполнить: вес одной коробки в килограммах. Число пишите так: 6,9</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Название</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Размер коробки, см</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Вес одной коробки, кг</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Ссылка</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Гайковерт 2500 Нм</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>42 × 32 × 14</t>
-        </is>
-      </c>
-      <c r="C5" s="21" t="n">
-        <v>69</v>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>https://adenis.su/tproduct/234640101402-gaikovert-2500-nm</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>Гайковерт 2200 Нм</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>42 × 32 × 14</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="n"/>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>https://adenis.su/tproduct/679794027832-gaikovert-2200-nm</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Гайковерт МТ 2100 Нм</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>42 × 32 × 14</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="n"/>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>https://adenis.su/tproduct/624931412933-gaikovert-mt-2100-nm</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>Гайковерт 2100 Нм</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>42 × 32 × 14</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="n"/>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>https://adenis.su/tproduct/844179078152-gaikovert-2100-nm</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Гайковерт 2000 Нм</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>42 × 32 × 14</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="n"/>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>https://adenis.su/tproduct/261441232642-gaikovert-2000-nm</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Гайковерт 1500 Нм</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>42 × 32 × 14</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="n"/>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>https://adenis.su/tproduct/643780222952-gaikovert-1500-nm</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Гайковерт 1400 Нм с оснасткой</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>38 × 30 × 14</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="n"/>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>https://adenis.su/tproduct/564940518092-gaikovert-1400-nm-s-osnastkoi</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>Гайковерт 1200 Нм с оснасткой</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>38 × 30 × 12</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="n"/>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>https://adenis.su/tproduct/133476019772-gaikovert-1200-nm-s-osnastkoi</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Гайковерт МТ 800 Нм</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>42 × 32 × 14</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="n"/>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>https://adenis.su/tproduct/950709964723-gaikovert-mt-800-nm</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="22" t="inlineStr">
-        <is>
-          <t>В модели 2500 уже стоит 69 — это цифра с листочка. Если это был вес всей партии, а не одной коробки, сотрите её и впишите вес одной коробки.</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="n"/>
-      <c r="C15" s="23" t="n"/>
-      <c r="D15" s="23" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A15:D15"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId9"/>
-  </hyperlinks>
-  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>